--- a/Eval_results/District_stats/global/summary.xlsx
+++ b/Eval_results/District_stats/global/summary.xlsx
@@ -476,29 +476,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>丰台区</t>
+          <t>Fengtai</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84.914142370224</v>
+        <v>35.83884835243225</v>
       </c>
       <c r="D2" t="n">
-        <v>64.38515675067902</v>
+        <v>125.6214842647314</v>
       </c>
       <c r="E2" t="n">
-        <v>4.325466156005859</v>
+        <v>98.29898071289062</v>
       </c>
       <c r="F2" t="n">
-        <v>153.6247652769089</v>
+        <v>259.7593133300543</v>
       </c>
       <c r="G2" t="n">
-        <v>84914142370.224</v>
+        <v>35838848352.43225</v>
       </c>
       <c r="H2" t="n">
-        <v>64.38515675067902</v>
+        <v>125.6214842647314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006179237365722656</v>
+        <v>0.1404271153041295</v>
       </c>
     </row>
     <row r="3">
@@ -507,29 +507,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>剩余五区</t>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.290531605482101</v>
+        <v>1.316506274044514</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8585612438619137</v>
+        <v>0.2631184896454215</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06119410274550319</v>
+        <v>3.1829833984375</v>
       </c>
       <c r="F3" t="n">
-        <v>4.493164464365691</v>
+        <v>4.762608162127435</v>
       </c>
       <c r="G3" t="n">
-        <v>5290531605.482101</v>
+        <v>1316506274.044514</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8585612438619137</v>
+        <v>0.2631184896454215</v>
       </c>
       <c r="I3" t="n">
-        <v>8.742014677929027e-05</v>
+        <v>0.004547119140625</v>
       </c>
     </row>
     <row r="4">
@@ -538,29 +538,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大兴区</t>
+          <t>Daxing</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.94913975894451</v>
+        <v>5.080098351929337</v>
       </c>
       <c r="D4" t="n">
-        <v>14.23802145570517</v>
+        <v>13.82848408818245</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5576896748971194</v>
+        <v>76.63259506225586</v>
       </c>
       <c r="F4" t="n">
-        <v>27.7448508895468</v>
+        <v>95.54117750236765</v>
       </c>
       <c r="G4" t="n">
-        <v>12949139758.94451</v>
+        <v>5080098351.929337</v>
       </c>
       <c r="H4" t="n">
-        <v>14.23802145570517</v>
+        <v>13.82848408818245</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007966995355673135</v>
+        <v>0.1094751358032227</v>
       </c>
     </row>
     <row r="5">
@@ -569,29 +569,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>房山区</t>
+          <t>Fangshan</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.816089957952499</v>
+        <v>-0.4521681368350983</v>
       </c>
       <c r="D5" t="n">
-        <v>19.84153747558594</v>
+        <v>17.00947342813015</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5569776147603989</v>
+        <v>104.8909187316895</v>
       </c>
       <c r="F5" t="n">
-        <v>28.21460504829884</v>
+        <v>121.4482240229845</v>
       </c>
       <c r="G5" t="n">
-        <v>7816089957.952498</v>
+        <v>-452168136.8350983</v>
       </c>
       <c r="H5" t="n">
-        <v>19.84153747558594</v>
+        <v>17.00947342813015</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007956823068005698</v>
+        <v>0.1498441696166992</v>
       </c>
     </row>
     <row r="6">
@@ -600,29 +600,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>昌平区</t>
+          <t>Changping</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.28409689664841</v>
+        <v>19.74009388685226</v>
       </c>
       <c r="D6" t="n">
-        <v>44.854233533144</v>
+        <v>71.65247827768326</v>
       </c>
       <c r="E6" t="n">
-        <v>3.824386738240719</v>
+        <v>178.5381317138672</v>
       </c>
       <c r="F6" t="n">
-        <v>103.9627171680331</v>
+        <v>269.9307038784027</v>
       </c>
       <c r="G6" t="n">
-        <v>55284096896.64841</v>
+        <v>19740093886.85226</v>
       </c>
       <c r="H6" t="n">
-        <v>44.854233533144</v>
+        <v>71.65247827768326</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00546340962605817</v>
+        <v>0.2550544738769531</v>
       </c>
     </row>
     <row r="7">
@@ -631,29 +631,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>朝阳区</t>
+          <t>Chaoyang</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>140.3005142211914</v>
+        <v>96.52459096908569</v>
       </c>
       <c r="D7" t="n">
-        <v>17.72890643496066</v>
+        <v>60.62578138709068</v>
       </c>
       <c r="E7" t="n">
-        <v>6.95556640625</v>
+        <v>90.75074195861816</v>
       </c>
       <c r="F7" t="n">
-        <v>164.9849870624021</v>
+        <v>247.9011143147945</v>
       </c>
       <c r="G7" t="n">
-        <v>140300514221.1914</v>
+        <v>96524590969.08569</v>
       </c>
       <c r="H7" t="n">
-        <v>17.72890643496066</v>
+        <v>60.62578138709068</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009936523437500001</v>
+        <v>0.1296439170837402</v>
       </c>
     </row>
     <row r="8">
@@ -662,29 +662,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>海淀区</t>
+          <t>Haidian</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68.60947704315186</v>
+        <v>12.29104925692081</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.188639540225267</v>
+        <v>20.40055428445339</v>
       </c>
       <c r="E8" t="n">
-        <v>2.413606584072113</v>
+        <v>8.86235237121582</v>
       </c>
       <c r="F8" t="n">
-        <v>64.8344440869987</v>
+        <v>41.55395591259003</v>
       </c>
       <c r="G8" t="n">
-        <v>68609477043.15185</v>
+        <v>12291049256.92081</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.188639540225267</v>
+        <v>20.40055428445339</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003448009405817304</v>
+        <v>0.01266050338745117</v>
       </c>
     </row>
     <row r="9">
@@ -693,29 +693,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>通州区</t>
+          <t>Tongzhou</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.767954379320145</v>
+        <v>1.532399985939264</v>
       </c>
       <c r="D9" t="n">
-        <v>1.456803426146507</v>
+        <v>8.200358346104622</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4186566835269332</v>
+        <v>41.57772064208984</v>
       </c>
       <c r="F9" t="n">
-        <v>11.64341448899359</v>
+        <v>51.31047897413373</v>
       </c>
       <c r="G9" t="n">
-        <v>9767954379.320145</v>
+        <v>1532399985.939264</v>
       </c>
       <c r="H9" t="n">
-        <v>1.456803426146507</v>
+        <v>8.200358346104622</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005980809764670474</v>
+        <v>0.05939674377441406</v>
       </c>
     </row>
     <row r="10">
@@ -724,29 +724,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>顺义区</t>
+          <t>Shunyi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.722876392304897</v>
+        <v>2.406438246369362</v>
       </c>
       <c r="D10" t="n">
-        <v>5.375667721033096</v>
+        <v>2.111157357692719</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05941391200758517</v>
+        <v>88.93394470214844</v>
       </c>
       <c r="F10" t="n">
-        <v>15.15795802534558</v>
+        <v>93.45154030621052</v>
       </c>
       <c r="G10" t="n">
-        <v>9722876392.304897</v>
+        <v>2406438246.369362</v>
       </c>
       <c r="H10" t="n">
-        <v>5.375667721033096</v>
+        <v>2.111157357692719</v>
       </c>
       <c r="I10" t="n">
-        <v>8.487701715369309e-05</v>
+        <v>0.1270484924316406</v>
       </c>
     </row>
   </sheetData>
